--- a/sampleprojects/CorporateTax/excel/states/NJ_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/NJ_corp.xlsx
@@ -71,7 +71,7 @@
     <t>apportionment.has_economic_nexus == true AND apportionment.state_code == "NJ"</t>
   </si>
   <si>
-    <t>*</t>
+    <t>-</t>
   </si>
   <si>
     <t>ACTIONS: COMMENTS</t>
